--- a/JANUARY 2026/Outstanding Bar/BLACK COFFEE ROASTERS JANUARY 2026 OUTSTANDING.xlsx
+++ b/JANUARY 2026/Outstanding Bar/BLACK COFFEE ROASTERS JANUARY 2026 OUTSTANDING.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17020"/>
+    <workbookView windowWidth="16600" windowHeight="17020"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BLACK COFFEE ROASTERS (Coffee)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,37 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_2CA52BA929A0482783BE75BE2714DF17" descr="PHOTO-2026-01-10-19-10-53"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect t="6402" r="2919" b="7022"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="8416290" y="-163195"/>
-          <a:ext cx="5622290" cy="8784590"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -284,7 +253,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -378,6 +347,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,64 +705,64 @@
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1110,6 +1085,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>29210</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3114675</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1998345</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_2CA52BA929A0482783BE75BE2714DF17" descr="PHOTO-2026-01-10-19-10-53"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect t="6402" r="2919" b="7022"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6630670" y="-328295"/>
+          <a:ext cx="1974215" cy="3085465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1383,7 +1402,7 @@
     <col min="8" max="8" width="15.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="16" customHeight="1" spans="1:8">
+    <row r="1" ht="16" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="158" customHeight="1" spans="1:8">
+    <row r="2" ht="158" customHeight="1" spans="1:8">
       <c r="A2" s="4">
         <v>46029</v>
       </c>
@@ -1425,10 +1444,7 @@
       <c r="E2" s="11">
         <v>280000</v>
       </c>
-      <c r="F2" s="12" t="str">
-        <f>_xlfn.DISPIMG("ID_2CA52BA929A0482783BE75BE2714DF17",1)</f>
-        <v>=DISPIMG("ID_2CA52BA929A0482783BE75BE2714DF17",1)</v>
-      </c>
+      <c r="F2" s="12"/>
       <c r="G2" s="11">
         <f>SUM(D2*E2)</f>
         <v>5600000</v>
@@ -1437,7 +1453,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="155.75" customHeight="1" spans="1:8">
+    <row r="3" ht="155.75" customHeight="1" spans="1:7">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
@@ -1448,9 +1464,8 @@
         <f>SUM(D3*E3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="1"/>
     </row>
-    <row r="4" customFormat="1" ht="23" customHeight="1" spans="1:8">
+    <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
@@ -1463,7 +1478,6 @@
         <v>5600000</v>
       </c>
       <c r="G4" s="14"/>
-      <c r="H4" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1471,6 +1485,8 @@
     <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>